--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_17-03-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_17-03-2026.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£23.87</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>£10.15</t>
+          <t>£11.67</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>£12.55</t>
+          <t>£14.42</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>£14.83</t>
+          <t>£17.53</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>£15.77</t>
+          <t>£18.37</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>£19.71</t>
+          <t>£23.65</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>£46.64</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>£22.00</t>
+          <t>£24.74</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>£22.11</t>
+          <t>£25.42</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>£25.12</t>
+          <t>£27.64</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>£27.44</t>
+          <t>£28.87</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>£26.49</t>
+          <t>£30.30</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>£32.40</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://build4less.co.uk/products/110mm-celotex-xr4110-2-4m-x-1-2m</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>£32.40</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.building-supplies-online.co.uk/products/celotex-xr4000-insulation-pitched-roof-board-1200-x-2400mm?variant=55597620494720</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>£32.13</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationuk.co.uk/products/110mm-celotex-xr4110-pir-insulation-board-2400mm-x-1200mm-x-110mm</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>£32.42</t>
+          <t>£36.76</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>£32.75</t>
+          <t>£36.75</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>£38.80</t>
+          <t>£50.00</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>£86.21</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>£39.81</t>
+          <t>£44.93</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>£9008.4</t>
+          <t>£9105.12</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Error: could not convert string to float: '1,035.75'</t>
+          <t>Error: could not convert string to float: '1,037.11'</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>£28.33</t>
+          <t>£32.58</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>£32.69</t>
+          <t>£36.52</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>£35.92</t>
+          <t>£39.12</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>£44.16</t>
+          <t>£48.95</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>£43.59</t>
+          <t>£47.42</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>£43.14</t>
+          <t>£45.71</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£48.37</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>£1224.64</t>
+          <t>£1408.0</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>£1377.12</t>
+          <t>£1583.52</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
